--- a/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:39</t>
+          <t>2026-10-14 00:25:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:41</t>
+          <t>2026-10-14 00:25:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:42</t>
+          <t>2026-10-14 00:25:13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:43</t>
+          <t>2026-10-14 00:25:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:43</t>
+          <t>2026-10-14 00:25:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:43</t>
+          <t>2026-10-14 00:25:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:43</t>
+          <t>2026-10-14 00:25:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:43</t>
+          <t>2026-10-14 00:25:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:10</t>
+          <t>2026-10-14 00:58:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:12</t>
+          <t>2026-10-14 00:58:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:13</t>
+          <t>2026-10-14 00:58:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:14</t>
+          <t>2026-10-14 00:58:58</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:14</t>
+          <t>2026-10-14 00:58:58</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:14</t>
+          <t>2026-10-14 00:58:58</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:14</t>
+          <t>2026-10-14 00:58:58</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:14</t>
+          <t>2026-10-14 00:58:58</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.43%753,000</t>
+          <t>9.58%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>9.58%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.68%249,000</t>
+          <t>5.75%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5545</v>
+        <v>5520</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.03%166,000</t>
+          <t>4.70%166,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10060</v>
+        <v>10005</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.12%79,000</t>
+          <t>4.06%79,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1180</v>
+        <v>349</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.87%625,000</t>
+          <t>3.94%2,416,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>625000</v>
+        <v>2416000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1775</v>
+        <v>1185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.79%404,000</t>
+          <t>3.77%625,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>404000</v>
+        <v>625000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6990</v>
+        <v>7070</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.67%104,000</t>
+          <t>3.71%104,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>319</v>
+        <v>1785</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.61%2,416,000</t>
+          <t>3.66%404,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.66%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2416000</v>
+        <v>404000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.47%6070</t>
+          <t>-4.78%5780</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.47%</t>
+          <t>-4.78%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6070</v>
+        <v>5780</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.30%103,000</t>
+          <t>3.19%103,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-7.4%488</t>
+          <t>-1.54%480.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>488</v>
+        <v>480.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.85%1,096,000</t>
+          <t>2.73%1,096,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.92%2725</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2725</v>
+        <v>8245</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.41%161,600</t>
+          <t>2.44%59,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>161600</v>
+        <v>59000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8095</v>
+        <v>747</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.36%59,000</t>
+          <t>2.35%621,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>59000</v>
+        <v>621000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+5.69%2880</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>740</v>
+        <v>2880</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.33%621,000</t>
+          <t>2.25%161,600</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>621000</v>
+        <v>161600</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:54</t>
+          <t>2026-10-14 21:53:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1170</v>
+        <v>1260</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.05%337,000</t>
+          <t>2.01%337,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-7.18%161.5</t>
+          <t>+1.25%243</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.18%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>161.5</v>
+        <v>243</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.97%2,293,000</t>
+          <t>1.98%1,616,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2293000</v>
+        <v>1616000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.84%240</t>
+          <t>+2.17%165</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.95%1,616,000</t>
+          <t>1.89%2,293,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1616000</v>
+        <v>2293000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5.39%5700</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.39%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5700</v>
+        <v>1430</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.81%61,000</t>
+          <t>1.85%251,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>61000</v>
+        <v>251000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1440</v>
+        <v>17500</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.78%251,000</t>
+          <t>1.80%20,300</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>251000</v>
+        <v>20300</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,34 +1724,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>-1.49%5615</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17350</v>
+        <v>5615</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.77%20,300</t>
+          <t>1.78%61,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>20300</v>
+        <v>61000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2195</v>
+        <v>2115</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>0%1965</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2200</v>
+        <v>1965</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.73%148,000</t>
+          <t>1.69%168,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>148000</v>
+        <v>168000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-4.38%1965</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.38%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1965</v>
+        <v>2250</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.70%168,000</t>
+          <t>1.66%148,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>168000</v>
+        <v>148000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.82%599</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>599</v>
+        <v>2050</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.52%485,000</t>
+          <t>1.48%142,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>485000</v>
+        <v>142000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>+4.67%627</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2040</v>
+        <v>627</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.49%142,000</t>
+          <t>1.48%485,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>142000</v>
+        <v>485000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.89%1040</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1040</v>
+        <v>6880</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.39%266,000</t>
+          <t>1.41%38,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>266000</v>
+        <v>38000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>+0.96%1050</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7275</v>
+        <v>1050</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.37%38,000</t>
+          <t>1.41%266,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>38000</v>
+        <v>266000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1655</v>
+        <v>1735</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.22%143,000</t>
+          <t>1.21%143,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:56</t>
+          <t>2026-10-14 21:53:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.05%806</t>
+          <t>+5.96%854</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>806</v>
+        <v>854</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.31%323</t>
+          <t>0%323</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.14%718,000</t>
+          <t>1.18%718,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.06%1,474,000</t>
+          <t>1.07%1,474,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2891中信金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.09%795</t>
+          <t>-0.28%71.4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>795</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.01%252,000</t>
+          <t>1.02%2,781,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>252000</v>
+        <v>2781000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.31%211.5</t>
+          <t>+7.67%856</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+7.67%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>211.5</v>
+        <v>856</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.97%906,000</t>
+          <t>1.02%252,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>906000</v>
+        <v>252000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2891中信金</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+2.58%71.6</t>
+          <t>+2.13%216</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>71.59999999999999</v>
+        <v>216</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.96%2,781,000</t>
+          <t>0.98%906,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2781000</v>
+        <v>906000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.32%187</t>
+          <t>0%187</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.89%948,000</t>
+          <t>0.91%948,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.47%268.5</t>
+          <t>+3.54%278</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>268.5</v>
+        <v>278</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.87%650,000</t>
+          <t>0.89%650,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.14%355.5</t>
+          <t>+0.14%356</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>355.5</v>
+        <v>356</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.85%484,000</t>
+          <t>0.88%484,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%797</t>
+          <t>+1.76%811</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.80%204,000</t>
+          <t>0.83%204,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.24%71.4</t>
+          <t>+0.28%71.6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.80%2,255,500</t>
+          <t>0.82%2,255,500</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.3%1635</t>
+          <t>+3.36%1690</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+3.36%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1635</v>
+        <v>1690</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.74%91,000</t>
+          <t>0.76%91,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.09%46.5</t>
+          <t>+1.72%47.3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>46.5</v>
+        <v>47.3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.67%2,962,622</t>
+          <t>0.70%2,962,622</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.4%2810</t>
+          <t>+2.31%2875</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.31%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2810</v>
+        <v>2875</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.62%44,000</t>
+          <t>0.63%44,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.64%2210</t>
+          <t>-0.68%2195</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2210</v>
+        <v>2195</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.60%54,000</t>
+          <t>0.61%54,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:57</t>
+          <t>2026-10-14 21:53:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>+5.42%603</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2260</v>
+        <v>603</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.56%48,336</t>
+          <t>0.57%195,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>48336</v>
+        <v>195000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:58</t>
+          <t>2026-10-14 21:53:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.21%572</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>572</v>
+        <v>2235</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.56%195,000</t>
+          <t>0.56%48,336</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>195000</v>
+        <v>48336</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:58</t>
+          <t>2026-10-14 21:53:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1715</v>
+        <v>1685</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.49%58,000</t>
+          <t>0.51%58,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:58</t>
+          <t>2026-10-14 21:53:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.84%478.5</t>
+          <t>-0.52%476</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>478.5</v>
+        <v>476</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:58</t>
+          <t>2026-10-14 21:53:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.67%838</t>
+          <t>+1.79%853</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.40%95,000</t>
+          <t>0.41%95,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:58:58</t>
+          <t>2026-10-14 21:53:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-5.51%1630</t>
+          <t>+0.61%1640</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:26</t>
+          <t>2026-10-14 22:01:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:27</t>
+          <t>2026-10-14 22:01:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:28</t>
+          <t>2026-10-14 22:01:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:30</t>
+          <t>2026-10-14 22:01:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:30</t>
+          <t>2026-10-14 22:01:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:30</t>
+          <t>2026-10-14 22:01:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:30</t>
+          <t>2026-10-14 22:01:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:30</t>
+          <t>2026-10-14 22:01:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:08</t>
+          <t>2026-10-14 22:31:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:10</t>
+          <t>2026-10-14 22:31:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:11</t>
+          <t>2026-10-14 22:31:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:12</t>
+          <t>2026-10-14 22:31:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:12</t>
+          <t>2026-10-14 22:31:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:12</t>
+          <t>2026-10-14 22:31:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:12</t>
+          <t>2026-10-14 22:31:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:12</t>
+          <t>2026-10-14 22:31:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
